--- a/dungeon-of-darkness/ドキュメント/イベント一覧.xlsx
+++ b/dungeon-of-darkness/ドキュメント/イベント一覧.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="402">
   <si>
     <t>フロア</t>
     <phoneticPr fontId="1"/>
@@ -4446,6 +4446,10 @@
     <rPh sb="14" eb="16">
       <t>ケイコク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェック</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4908,7 +4912,7 @@
     <col min="8" max="8" width="6.109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39" customHeight="1">
@@ -4940,6 +4944,9 @@
       <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="K1" s="4" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="4">
@@ -4962,7 +4969,7 @@
         <v>11</v>
       </c>
       <c r="J2" s="6"/>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -4987,7 +4994,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="6"/>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5012,7 +5019,7 @@
         <v>11</v>
       </c>
       <c r="J4" s="6"/>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5037,7 +5044,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5072,7 +5079,7 @@
       <c r="J6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5107,7 +5114,7 @@
       <c r="J7" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5142,7 +5149,7 @@
       <c r="J8" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5175,7 +5182,7 @@
         <v>11</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5208,7 +5215,7 @@
         <v>11</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5243,7 +5250,7 @@
       <c r="J11" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5278,7 +5285,7 @@
       <c r="J12" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5313,7 +5320,7 @@
       <c r="J13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5348,7 +5355,7 @@
       <c r="J14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5383,7 +5390,7 @@
       <c r="J15" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5418,7 +5425,7 @@
       <c r="J16" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5453,7 +5460,7 @@
       <c r="J17" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5488,7 +5495,7 @@
       <c r="J18" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5523,7 +5530,7 @@
       <c r="J19" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5558,7 +5565,7 @@
       <c r="J20" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5593,7 +5600,7 @@
       <c r="J21" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5628,7 +5635,7 @@
       <c r="J22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5663,7 +5670,7 @@
       <c r="J23" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="4" t="s">
         <v>262</v>
       </c>
     </row>
@@ -5698,7 +5705,7 @@
       <c r="J24" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="4" t="s">
         <v>262</v>
       </c>
     </row>
@@ -5733,7 +5740,7 @@
       <c r="J25" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="4" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5766,7 +5773,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="6"/>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="4" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5801,7 +5808,7 @@
       <c r="J27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="4" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5836,7 +5843,7 @@
       <c r="J28" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5871,7 +5878,7 @@
       <c r="J29" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" s="4" t="s">
         <v>164</v>
       </c>
     </row>
@@ -5906,7 +5913,7 @@
       <c r="J30" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="4" t="s">
         <v>164</v>
       </c>
     </row>
@@ -5941,7 +5948,7 @@
       <c r="J31" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="4" t="s">
         <v>164</v>
       </c>
     </row>
@@ -5974,7 +5981,7 @@
         <v>53</v>
       </c>
       <c r="J32" s="6"/>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6009,7 +6016,7 @@
       <c r="J33" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6044,7 +6051,7 @@
       <c r="J34" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6079,7 +6086,7 @@
       <c r="J35" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6114,7 +6121,7 @@
       <c r="J36" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6149,7 +6156,7 @@
       <c r="J37" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6184,7 +6191,7 @@
       <c r="J38" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6219,7 +6226,7 @@
       <c r="J39" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6254,7 +6261,7 @@
       <c r="J40" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6289,7 +6296,7 @@
       <c r="J41" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6324,7 +6331,7 @@
       <c r="J42" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6359,7 +6366,7 @@
       <c r="J43" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6394,7 +6401,7 @@
       <c r="J44" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="K44" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6429,7 +6436,7 @@
       <c r="J45" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="K45" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6464,7 +6471,7 @@
       <c r="J46" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K46" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6499,7 +6506,7 @@
       <c r="J47" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="K47" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6534,7 +6541,7 @@
       <c r="J48" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K48" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6569,7 +6576,7 @@
       <c r="J49" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6604,7 +6611,7 @@
       <c r="J50" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="K50" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6637,7 +6644,7 @@
         <v>11</v>
       </c>
       <c r="J51" s="6"/>
-      <c r="K51" s="1" t="s">
+      <c r="K51" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6670,7 +6677,7 @@
         <v>11</v>
       </c>
       <c r="J52" s="6"/>
-      <c r="K52" s="1" t="s">
+      <c r="K52" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6705,7 +6712,7 @@
       <c r="J53" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="K53" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6740,7 +6747,7 @@
       <c r="J54" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6775,7 +6782,7 @@
       <c r="J55" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6810,7 +6817,7 @@
       <c r="J56" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K56" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6845,7 +6852,7 @@
       <c r="J57" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6880,7 +6887,7 @@
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K58" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6915,7 +6922,7 @@
       <c r="J59" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K59" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6950,7 +6957,7 @@
       <c r="J60" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="K60" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6985,7 +6992,7 @@
       <c r="J61" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K61" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7020,7 +7027,7 @@
       <c r="J62" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="K62" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7055,7 +7062,7 @@
       <c r="J63" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="K63" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7090,7 +7097,7 @@
       <c r="J64" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="K64" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7125,7 +7132,7 @@
       <c r="J65" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K65" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7160,7 +7167,7 @@
       <c r="J66" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="K66" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7195,7 +7202,7 @@
       <c r="J67" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7230,7 +7237,7 @@
       <c r="J68" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="K68" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7265,7 +7272,7 @@
       <c r="J69" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K69" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7300,7 +7307,7 @@
       <c r="J70" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="K70" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7333,7 +7340,7 @@
         <v>11</v>
       </c>
       <c r="J71" s="6"/>
-      <c r="K71" s="1" t="s">
+      <c r="K71" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7368,7 +7375,7 @@
       <c r="J72" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K72" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7403,7 +7410,7 @@
       <c r="J73" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="K73" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7438,7 +7445,7 @@
       <c r="J74" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="K74" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7473,7 +7480,7 @@
       <c r="J75" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="K75" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7508,7 +7515,7 @@
       <c r="J76" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K76" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7543,7 +7550,7 @@
       <c r="J77" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="K77" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7578,7 +7585,7 @@
       <c r="J78" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="K78" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7613,7 +7620,7 @@
       <c r="J79" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K79" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7648,7 +7655,7 @@
       <c r="J80" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K80" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7683,7 +7690,7 @@
       <c r="J81" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="K81" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7718,7 +7725,7 @@
       <c r="J82" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="K82" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7753,7 +7760,7 @@
       <c r="J83" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="K83" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7788,7 +7795,7 @@
       <c r="J84" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K84" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7823,7 +7830,7 @@
       <c r="J85" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K85" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7858,7 +7865,7 @@
       <c r="J86" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K86" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7893,7 +7900,7 @@
       <c r="J87" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K87" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7928,7 +7935,7 @@
       <c r="J88" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K88" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7963,7 +7970,7 @@
       <c r="J89" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="K89" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -7998,7 +8005,7 @@
       <c r="J90" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="K90" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8033,7 +8040,7 @@
       <c r="J91" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="K91" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8068,7 +8075,7 @@
       <c r="J92" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K92" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8103,7 +8110,7 @@
       <c r="J93" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K93" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8136,7 +8143,7 @@
         <v>11</v>
       </c>
       <c r="J94" s="6"/>
-      <c r="K94" s="1" t="s">
+      <c r="K94" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8171,7 +8178,7 @@
       <c r="J95" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="K95" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8206,7 +8213,7 @@
       <c r="J96" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="K96" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8241,7 +8248,7 @@
       <c r="J97" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="K97" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8276,7 +8283,7 @@
       <c r="J98" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="K98" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8311,7 +8318,7 @@
       <c r="J99" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="K99" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8346,7 +8353,7 @@
       <c r="J100" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="K100" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8381,7 +8388,7 @@
       <c r="J101" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K101" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8416,7 +8423,7 @@
       <c r="J102" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K102" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8451,7 +8458,7 @@
       <c r="J103" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K103" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8486,7 +8493,7 @@
       <c r="J104" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K104" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8521,7 +8528,7 @@
       <c r="J105" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K105" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8556,7 +8563,7 @@
       <c r="J106" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="K106" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8591,7 +8598,7 @@
       <c r="J107" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K107" s="1" t="s">
+      <c r="K107" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8626,7 +8633,7 @@
       <c r="J108" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K108" s="1" t="s">
+      <c r="K108" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8661,7 +8668,7 @@
       <c r="J109" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K109" s="1" t="s">
+      <c r="K109" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8696,7 +8703,7 @@
       <c r="J110" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K110" s="1" t="s">
+      <c r="K110" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8731,7 +8738,7 @@
       <c r="J111" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K111" s="1" t="s">
+      <c r="K111" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8766,7 +8773,7 @@
       <c r="J112" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K112" s="1" t="s">
+      <c r="K112" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8801,7 +8808,7 @@
       <c r="J113" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K113" s="1" t="s">
+      <c r="K113" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8834,7 +8841,7 @@
         <v>71</v>
       </c>
       <c r="J114" s="10"/>
-      <c r="K114" s="1" t="s">
+      <c r="K114" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8867,7 +8874,7 @@
         <v>71</v>
       </c>
       <c r="J115" s="10"/>
-      <c r="K115" s="1" t="s">
+      <c r="K115" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8902,7 +8909,7 @@
       <c r="J116" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K116" s="1" t="s">
+      <c r="K116" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8937,7 +8944,7 @@
       <c r="J117" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K117" s="1" t="s">
+      <c r="K117" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -8972,7 +8979,7 @@
       <c r="J118" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K118" s="1" t="s">
+      <c r="K118" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9007,7 +9014,7 @@
       <c r="J119" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K119" s="1" t="s">
+      <c r="K119" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9042,7 +9049,7 @@
       <c r="J120" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="K120" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9077,7 +9084,7 @@
       <c r="J121" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="K121" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9112,7 +9119,7 @@
       <c r="J122" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K122" s="1" t="s">
+      <c r="K122" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9147,7 +9154,7 @@
       <c r="J123" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K123" s="1" t="s">
+      <c r="K123" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9182,7 +9189,7 @@
       <c r="J124" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K124" s="1" t="s">
+      <c r="K124" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9217,7 +9224,7 @@
       <c r="J125" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K125" s="1" t="s">
+      <c r="K125" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9252,7 +9259,7 @@
       <c r="J126" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K126" s="1" t="s">
+      <c r="K126" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9287,7 +9294,7 @@
       <c r="J127" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K127" s="1" t="s">
+      <c r="K127" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9322,7 +9329,7 @@
       <c r="J128" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K128" s="1" t="s">
+      <c r="K128" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9357,7 +9364,7 @@
       <c r="J129" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K129" s="1" t="s">
+      <c r="K129" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9392,7 +9399,7 @@
       <c r="J130" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="K130" s="1" t="s">
+      <c r="K130" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9427,7 +9434,7 @@
       <c r="J131" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K131" s="1" t="s">
+      <c r="K131" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9462,7 +9469,7 @@
       <c r="J132" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K132" s="1" t="s">
+      <c r="K132" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9497,7 +9504,7 @@
       <c r="J133" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="K133" s="1" t="s">
+      <c r="K133" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9532,7 +9539,7 @@
       <c r="J134" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K134" s="1" t="s">
+      <c r="K134" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9567,7 +9574,7 @@
       <c r="J135" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K135" s="1" t="s">
+      <c r="K135" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9600,7 +9607,7 @@
         <v>71</v>
       </c>
       <c r="J136" s="6"/>
-      <c r="K136" s="1" t="s">
+      <c r="K136" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9635,7 +9642,7 @@
       <c r="J137" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="K137" s="1" t="s">
+      <c r="K137" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9670,7 +9677,7 @@
       <c r="J138" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K138" s="1" t="s">
+      <c r="K138" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9705,7 +9712,7 @@
       <c r="J139" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K139" s="1" t="s">
+      <c r="K139" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9740,7 +9747,7 @@
       <c r="J140" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="K140" s="1" t="s">
+      <c r="K140" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9775,7 +9782,7 @@
       <c r="J141" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="K141" s="1" t="s">
+      <c r="K141" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9810,7 +9817,7 @@
       <c r="J142" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K142" s="1" t="s">
+      <c r="K142" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9845,7 +9852,7 @@
       <c r="J143" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K143" s="1" t="s">
+      <c r="K143" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9880,7 +9887,7 @@
       <c r="J144" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K144" s="1" t="s">
+      <c r="K144" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9915,7 +9922,7 @@
       <c r="J145" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K145" s="1" t="s">
+      <c r="K145" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9950,7 +9957,7 @@
       <c r="J146" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K146" s="1" t="s">
+      <c r="K146" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9985,7 +9992,7 @@
       <c r="J147" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K147" s="1" t="s">
+      <c r="K147" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10020,7 +10027,7 @@
       <c r="J148" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K148" s="1" t="s">
+      <c r="K148" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10055,7 +10062,7 @@
       <c r="J149" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K149" s="1" t="s">
+      <c r="K149" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10090,7 +10097,7 @@
       <c r="J150" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K150" s="1" t="s">
+      <c r="K150" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10125,7 +10132,7 @@
       <c r="J151" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K151" s="1" t="s">
+      <c r="K151" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10160,7 +10167,7 @@
       <c r="J152" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K152" s="1" t="s">
+      <c r="K152" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10195,7 +10202,7 @@
       <c r="J153" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="K153" s="1" t="s">
+      <c r="K153" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10230,7 +10237,7 @@
       <c r="J154" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="K154" s="1" t="s">
+      <c r="K154" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10265,7 +10272,7 @@
       <c r="J155" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="K155" s="1" t="s">
+      <c r="K155" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10300,7 +10307,7 @@
       <c r="J156" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="K156" s="1" t="s">
+      <c r="K156" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10333,7 +10340,7 @@
         <v>11</v>
       </c>
       <c r="J157" s="6"/>
-      <c r="K157" s="1" t="s">
+      <c r="K157" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10366,7 +10373,7 @@
         <v>11</v>
       </c>
       <c r="J158" s="6"/>
-      <c r="K158" s="1" t="s">
+      <c r="K158" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10399,7 +10406,7 @@
         <v>11</v>
       </c>
       <c r="J159" s="6"/>
-      <c r="K159" s="1" t="s">
+      <c r="K159" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10434,7 +10441,7 @@
       <c r="J160" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="K160" s="1" t="s">
+      <c r="K160" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10467,7 +10474,7 @@
         <v>11</v>
       </c>
       <c r="J161" s="6"/>
-      <c r="K161" s="1" t="s">
+      <c r="K161" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10502,7 +10509,7 @@
       <c r="J162" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="K162" s="1" t="s">
+      <c r="K162" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10537,7 +10544,7 @@
       <c r="J163" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K163" s="1" t="s">
+      <c r="K163" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10572,7 +10579,7 @@
       <c r="J164" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K164" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10607,7 +10614,7 @@
       <c r="J165" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K165" s="1" t="s">
+      <c r="K165" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10642,7 +10649,7 @@
       <c r="J166" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K166" s="1" t="s">
+      <c r="K166" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10675,7 +10682,7 @@
         <v>53</v>
       </c>
       <c r="J167" s="6"/>
-      <c r="K167" s="1" t="s">
+      <c r="K167" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10710,7 +10717,7 @@
       <c r="J168" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="K168" s="1" t="s">
+      <c r="K168" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10745,7 +10752,7 @@
       <c r="J169" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="K169" s="1" t="s">
+      <c r="K169" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10780,7 +10787,7 @@
       <c r="J170" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="K170" s="1" t="s">
+      <c r="K170" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10815,7 +10822,7 @@
       <c r="J171" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="K171" s="1" t="s">
+      <c r="K171" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10850,7 +10857,7 @@
       <c r="J172" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="K172" s="1" t="s">
+      <c r="K172" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10885,7 +10892,7 @@
       <c r="J173" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="K173" s="1" t="s">
+      <c r="K173" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10920,7 +10927,7 @@
       <c r="J174" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="K174" s="1" t="s">
+      <c r="K174" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10955,7 +10962,7 @@
       <c r="J175" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K175" s="1" t="s">
+      <c r="K175" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -10990,7 +10997,7 @@
       <c r="J176" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="K176" s="1" t="s">
+      <c r="K176" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -11025,7 +11032,7 @@
       <c r="J177" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="K177" s="1" t="s">
+      <c r="K177" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -11060,7 +11067,7 @@
       <c r="J178" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K178" s="1" t="s">
+      <c r="K178" s="4" t="s">
         <v>153</v>
       </c>
     </row>
@@ -11095,7 +11102,7 @@
       <c r="J179" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K179" s="1" t="s">
+      <c r="K179" s="4" t="s">
         <v>153</v>
       </c>
     </row>
